--- a/Library/assets/sheets.xlsx
+++ b/Library/assets/sheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajri\OneDrive\Desktop\Library\Library-app\Library\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/piyushasthana/Documents/mcaet/Library-app/Library/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B85E4E9-59B3-4500-BF2A-404D3DEA37A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912021AE-5834-A64A-8B98-A6DD19B39FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="237">
   <si>
     <t>S. No.</t>
   </si>
@@ -765,6 +765,18 @@
   </si>
   <si>
     <t xml:space="preserve">Materials And Processes  in Manufactining </t>
+  </si>
+  <si>
+    <t>wew</t>
+  </si>
+  <si>
+    <t>eww</t>
+  </si>
+  <si>
+    <t>we</t>
+  </si>
+  <si>
+    <t>qw</t>
   </si>
 </sst>
 </file>
@@ -857,15 +869,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -880,6 +883,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1216,58 +1228,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O77"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="57" style="1" customWidth="1"/>
     <col min="4" max="4" width="44.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="55.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="36.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.77734375" style="1"/>
+    <col min="10" max="10" width="8.83203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-    </row>
-    <row r="3" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1297,7 +1309,7 @@
       <c r="M3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -1327,7 +1339,7 @@
       <c r="M4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1357,7 +1369,7 @@
       <c r="M5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1387,7 +1399,7 @@
       <c r="M6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -1417,7 +1429,7 @@
       <c r="M7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -1447,7 +1459,7 @@
       <c r="M8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -1477,7 +1489,7 @@
       <c r="M9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -1507,7 +1519,7 @@
       <c r="M10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -1537,7 +1549,7 @@
       <c r="M11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -1567,7 +1579,7 @@
       <c r="M12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -1597,7 +1609,7 @@
       <c r="M13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -1627,7 +1639,7 @@
       <c r="M14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -1657,7 +1669,7 @@
       <c r="M15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -1687,7 +1699,7 @@
       <c r="M16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -1714,7 +1726,7 @@
       <c r="M17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -1744,7 +1756,7 @@
       <c r="M18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -1774,7 +1786,7 @@
       <c r="M19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>18</v>
       </c>
@@ -1800,7 +1812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>19</v>
       </c>
@@ -1826,7 +1838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>20</v>
       </c>
@@ -1852,7 +1864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>21</v>
       </c>
@@ -1878,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>22</v>
       </c>
@@ -1904,7 +1916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>23</v>
       </c>
@@ -1930,7 +1942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>24</v>
       </c>
@@ -1957,7 +1969,7 @@
       </c>
       <c r="I26"/>
     </row>
-    <row r="27" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>25</v>
       </c>
@@ -1984,7 +1996,7 @@
       </c>
       <c r="I27"/>
     </row>
-    <row r="28" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>26</v>
       </c>
@@ -2011,7 +2023,7 @@
       </c>
       <c r="I28"/>
     </row>
-    <row r="29" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>27</v>
       </c>
@@ -2038,7 +2050,7 @@
       </c>
       <c r="I29"/>
     </row>
-    <row r="30" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>28</v>
       </c>
@@ -2065,7 +2077,7 @@
       </c>
       <c r="I30"/>
     </row>
-    <row r="31" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>29</v>
       </c>
@@ -2092,7 +2104,7 @@
       </c>
       <c r="I31"/>
     </row>
-    <row r="32" spans="1:15" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>30</v>
       </c>
@@ -2119,7 +2131,7 @@
       </c>
       <c r="I32"/>
     </row>
-    <row r="33" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>31</v>
       </c>
@@ -2146,7 +2158,7 @@
       </c>
       <c r="I33"/>
     </row>
-    <row r="34" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>32</v>
       </c>
@@ -2173,7 +2185,7 @@
       </c>
       <c r="I34"/>
     </row>
-    <row r="35" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>33</v>
       </c>
@@ -2200,7 +2212,7 @@
       </c>
       <c r="I35"/>
     </row>
-    <row r="36" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>34</v>
       </c>
@@ -2227,7 +2239,7 @@
       </c>
       <c r="I36"/>
     </row>
-    <row r="37" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>35</v>
       </c>
@@ -2254,7 +2266,7 @@
       </c>
       <c r="I37"/>
     </row>
-    <row r="38" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>36</v>
       </c>
@@ -2281,7 +2293,7 @@
       </c>
       <c r="I38"/>
     </row>
-    <row r="39" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>37</v>
       </c>
@@ -2308,7 +2320,7 @@
       </c>
       <c r="I39"/>
     </row>
-    <row r="40" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>38</v>
       </c>
@@ -2335,7 +2347,7 @@
       </c>
       <c r="I40"/>
     </row>
-    <row r="41" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>39</v>
       </c>
@@ -2362,7 +2374,7 @@
       </c>
       <c r="I41"/>
     </row>
-    <row r="42" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -2389,14 +2401,14 @@
       </c>
       <c r="I42"/>
     </row>
-    <row r="43" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>41</v>
       </c>
       <c r="B43" s="5">
         <v>12.3</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="14" t="s">
         <v>127</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2415,14 +2427,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>42</v>
       </c>
       <c r="B44" s="5">
         <v>12.3</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="13" t="s">
         <v>130</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2441,17 +2453,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>43</v>
       </c>
       <c r="B45" s="5">
         <v>12.3</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="13" t="s">
         <v>134</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -2460,47 +2472,47 @@
       <c r="F45" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="15" t="s">
         <v>137</v>
       </c>
       <c r="H45" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>44</v>
       </c>
       <c r="B46" s="5">
         <v>12.3</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="G46" s="18" t="s">
+      <c r="G46" s="15" t="s">
         <v>141</v>
       </c>
       <c r="H46" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>45</v>
       </c>
       <c r="B47" s="5">
         <v>12.3</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="13" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="12" t="s">
@@ -2519,7 +2531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -2529,7 +2541,7 @@
       <c r="C48" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="13" t="s">
         <v>145</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -2545,7 +2557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>47</v>
       </c>
@@ -2555,7 +2567,7 @@
       <c r="C49" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="13" t="s">
         <v>148</v>
       </c>
       <c r="E49" s="12" t="s">
@@ -2571,14 +2583,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>48</v>
       </c>
       <c r="B50" s="5">
         <v>12.3</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="13" t="s">
         <v>152</v>
       </c>
       <c r="D50" s="12" t="s">
@@ -2597,7 +2609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -2607,7 +2619,7 @@
       <c r="C51" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="13" t="s">
         <v>158</v>
       </c>
       <c r="E51" s="12" t="s">
@@ -2623,7 +2635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>50</v>
       </c>
@@ -2633,7 +2645,7 @@
       <c r="C52" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="13" t="s">
         <v>161</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -2642,14 +2654,14 @@
       <c r="F52" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="G52" s="18" t="s">
+      <c r="G52" s="15" t="s">
         <v>137</v>
       </c>
       <c r="H52" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>51</v>
       </c>
@@ -2659,7 +2671,7 @@
       <c r="C53" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="13" t="s">
         <v>164</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -2675,7 +2687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>52</v>
       </c>
@@ -2691,17 +2703,17 @@
       <c r="E54" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="F54" s="18" t="s">
+      <c r="F54" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G54" s="18" t="s">
+      <c r="G54" s="15" t="s">
         <v>14</v>
       </c>
       <c r="H54" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>53</v>
       </c>
@@ -2711,7 +2723,7 @@
       <c r="C55" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="13" t="s">
         <v>170</v>
       </c>
       <c r="E55" s="12" t="s">
@@ -2727,7 +2739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>54</v>
       </c>
@@ -2737,7 +2749,7 @@
       <c r="C56" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D56" s="16" t="s">
+      <c r="D56" s="13" t="s">
         <v>173</v>
       </c>
       <c r="E56" s="12" t="s">
@@ -2746,14 +2758,14 @@
       <c r="F56" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G56" s="18" t="s">
+      <c r="G56" s="15" t="s">
         <v>88</v>
       </c>
       <c r="H56" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>55</v>
       </c>
@@ -2763,7 +2775,7 @@
       <c r="C57" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="13" t="s">
         <v>176</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -2779,7 +2791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>56</v>
       </c>
@@ -2795,17 +2807,17 @@
       <c r="E58" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F58" s="18" t="s">
+      <c r="F58" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="G58" s="18" t="s">
+      <c r="G58" s="15" t="s">
         <v>88</v>
       </c>
       <c r="H58" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>57</v>
       </c>
@@ -2821,17 +2833,17 @@
       <c r="E59" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="F59" s="18" t="s">
+      <c r="F59" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="15" t="s">
         <v>88</v>
       </c>
       <c r="H59" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>58</v>
       </c>
@@ -2857,7 +2869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>59</v>
       </c>
@@ -2883,14 +2895,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>60</v>
       </c>
       <c r="B62" s="1">
         <v>14</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="16" t="s">
         <v>190</v>
       </c>
       <c r="D62" s="12" t="s">
@@ -2899,24 +2911,24 @@
       <c r="E62" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F62" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G62" s="19" t="s">
+      <c r="G62" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H62" s="19">
+      <c r="H62" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>61</v>
       </c>
       <c r="B63" s="1">
         <v>14</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="16" t="s">
         <v>193</v>
       </c>
       <c r="D63" s="12" t="s">
@@ -2925,43 +2937,43 @@
       <c r="E63" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="F63" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G63" s="19" t="s">
+      <c r="G63" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H63" s="19">
+      <c r="H63" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>62</v>
       </c>
       <c r="B64" s="1">
         <v>14</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="16" t="s">
         <v>193</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F64" s="19" t="s">
+      <c r="F64" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G64" s="19" t="s">
+      <c r="G64" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H64" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H64" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>63</v>
       </c>
@@ -2987,7 +2999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>64</v>
       </c>
@@ -3013,7 +3025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>65</v>
       </c>
@@ -3039,7 +3051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>66</v>
       </c>
@@ -3065,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>67</v>
       </c>
@@ -3075,23 +3087,23 @@
       <c r="C69" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D69" s="20" t="s">
+      <c r="D69" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="E69" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="F69" s="19" t="s">
+      <c r="F69" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G69" s="19" t="s">
+      <c r="G69" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H69" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H69" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>68</v>
       </c>
@@ -3101,23 +3113,23 @@
       <c r="C70" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D70" s="20" t="s">
+      <c r="D70" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="E70" s="19" t="s">
+      <c r="E70" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="F70" s="19" t="s">
+      <c r="F70" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G70" s="19" t="s">
+      <c r="G70" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H70" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H70" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>69</v>
       </c>
@@ -3143,7 +3155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>70</v>
       </c>
@@ -3153,49 +3165,49 @@
       <c r="C72" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D72" s="20" t="s">
+      <c r="D72" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="F72" s="19" t="s">
+      <c r="F72" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G72" s="19" t="s">
+      <c r="G72" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="H72" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H72" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>71</v>
       </c>
       <c r="B73" s="1">
         <v>14</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="C73" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="D73" s="20" t="s">
+      <c r="D73" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="E73" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="F73" s="19" t="s">
+      <c r="F73" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G73" s="19" t="s">
+      <c r="G73" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="H73" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H73" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>72</v>
       </c>
@@ -3205,7 +3217,7 @@
       <c r="C74" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="D74" s="20" t="s">
+      <c r="D74" s="17" t="s">
         <v>221</v>
       </c>
       <c r="E74" t="s">
@@ -3221,7 +3233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>73</v>
       </c>
@@ -3231,7 +3243,7 @@
       <c r="C75" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D75" s="20" t="s">
+      <c r="D75" s="17" t="s">
         <v>224</v>
       </c>
       <c r="E75" t="s">
@@ -3247,34 +3259,57 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>74</v>
       </c>
       <c r="B76" s="1">
         <v>14</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="D76" s="20" t="s">
+      <c r="D76" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="E76" s="19" t="s">
+      <c r="E76" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="F76" s="19" t="s">
+      <c r="F76" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="G76" s="19" t="s">
+      <c r="G76" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="H76" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
+      <c r="H76" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="4">
+        <v>77</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1222</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H77" s="1">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
